--- a/excel-files/CALOOCAN/CIELITO ZAMORA SENIOR HIGH SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/CIELITO ZAMORA SENIOR HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70481977-E1E3-4E7C-AEF4-AFCF36BB7EB7}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B7AF350-44F4-4BCD-9525-11672BBD3A10}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -736,6 +736,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -747,12 +753,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+    <row r="6" spans="1:8" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5337,12 +5337,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E81:E89 E71:E79 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E5 E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69" xr:uid="{91B2A1CE-E432-4197-B93E-56E94911FCF4}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5354,7 +5357,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5384,38 +5387,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5454,10 +5457,10 @@
       <c r="L2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>46</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5490,10 +5493,10 @@
       <c r="X2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>58</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -5648,7 +5651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5717,7 +5720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5786,7 +5789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5855,7 +5858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -5924,7 +5927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -5993,7 +5996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6062,7 +6065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6131,7 +6134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6144,7 +6147,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6213,7 +6216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6282,7 +6285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6351,7 +6354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6420,7 +6423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6489,7 +6492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6558,7 +6561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6627,7 +6630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6696,7 +6699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6710,7 +6713,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6779,7 +6782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6848,7 +6851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -6917,7 +6920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -6986,7 +6989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7055,7 +7058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7124,7 +7127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7193,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7262,7 +7265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7331,7 +7334,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="F32"/>
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7345,7 +7349,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7414,7 +7418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7483,7 +7487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7552,7 +7556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7621,7 +7625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7690,7 +7694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7759,7 +7763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7828,7 +7832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -7897,7 +7901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -7966,7 +7970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -7980,7 +7984,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8049,7 +8053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8118,7 +8122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8187,7 +8191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8256,7 +8260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8325,7 +8329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8394,7 +8398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8463,7 +8467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8532,7 +8536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8601,7 +8605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8615,7 +8619,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8684,7 +8688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8753,7 +8757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8822,7 +8826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -8891,7 +8895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -8960,7 +8964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9029,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9098,7 +9102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9167,7 +9171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9236,7 +9240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9250,7 +9254,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9293,7 +9297,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="12"/>
-      <c r="R63" s="10"/>
+      <c r="R63" s="1"/>
       <c r="S63" s="12"/>
       <c r="T63" s="12">
         <f t="shared" si="12"/>
@@ -9319,7 +9323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9362,7 +9366,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="12"/>
-      <c r="R64" s="10"/>
+      <c r="R64" s="1"/>
       <c r="S64" s="12"/>
       <c r="T64" s="12">
         <f t="shared" si="12"/>
@@ -9388,7 +9392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9431,7 +9435,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="12"/>
-      <c r="R65" s="10"/>
+      <c r="R65" s="1"/>
       <c r="S65" s="12"/>
       <c r="T65" s="12">
         <f t="shared" si="12"/>
@@ -9457,7 +9461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9500,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="12"/>
-      <c r="R66" s="10"/>
+      <c r="R66" s="1"/>
       <c r="S66" s="12"/>
       <c r="T66" s="12">
         <f t="shared" si="12"/>
@@ -9526,7 +9530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9569,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="Q67" s="12"/>
-      <c r="R67" s="10"/>
+      <c r="R67" s="1"/>
       <c r="S67" s="12"/>
       <c r="T67" s="12">
         <f t="shared" si="12"/>
@@ -9595,7 +9599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9638,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="12"/>
-      <c r="R68" s="10"/>
+      <c r="R68" s="1"/>
       <c r="S68" s="12"/>
       <c r="T68" s="12">
         <f t="shared" si="12"/>
@@ -9664,7 +9668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9707,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="12"/>
-      <c r="R69" s="10"/>
+      <c r="R69" s="1"/>
       <c r="S69" s="12"/>
       <c r="T69" s="12">
         <f t="shared" si="12"/>
@@ -9733,7 +9737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9776,7 +9780,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="12"/>
-      <c r="R70" s="10"/>
+      <c r="R70" s="1"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12">
         <f t="shared" ref="T70:T127" si="18">IF((P70-Q70)&lt;0,0,(P70-Q70))</f>
@@ -9802,7 +9806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9845,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="Q71" s="12"/>
-      <c r="R71" s="10"/>
+      <c r="R71" s="1"/>
       <c r="S71" s="12"/>
       <c r="T71" s="12">
         <f t="shared" si="18"/>
@@ -9871,7 +9875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -9885,7 +9889,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -9928,7 +9932,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="12"/>
-      <c r="R73" s="10"/>
+      <c r="R73" s="1"/>
       <c r="S73" s="12"/>
       <c r="T73" s="12">
         <f t="shared" si="18"/>
@@ -9954,7 +9958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -9997,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="Q74" s="12"/>
-      <c r="R74" s="10"/>
+      <c r="R74" s="1"/>
       <c r="S74" s="12"/>
       <c r="T74" s="12">
         <f t="shared" si="18"/>
@@ -10023,7 +10027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10066,7 +10070,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="12"/>
-      <c r="R75" s="10"/>
+      <c r="R75" s="1"/>
       <c r="S75" s="12"/>
       <c r="T75" s="12">
         <f t="shared" si="18"/>
@@ -10092,7 +10096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10135,7 +10139,7 @@
         <v>0</v>
       </c>
       <c r="Q76" s="12"/>
-      <c r="R76" s="10"/>
+      <c r="R76" s="1"/>
       <c r="S76" s="12"/>
       <c r="T76" s="12">
         <f t="shared" si="18"/>
@@ -10161,7 +10165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10204,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="Q77" s="12"/>
-      <c r="R77" s="10"/>
+      <c r="R77" s="1"/>
       <c r="S77" s="12"/>
       <c r="T77" s="12">
         <f t="shared" si="18"/>
@@ -10230,7 +10234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10273,7 +10277,7 @@
         <v>0</v>
       </c>
       <c r="Q78" s="12"/>
-      <c r="R78" s="10"/>
+      <c r="R78" s="1"/>
       <c r="S78" s="12"/>
       <c r="T78" s="12">
         <f t="shared" si="18"/>
@@ -10299,7 +10303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10342,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="Q79" s="12"/>
-      <c r="R79" s="10"/>
+      <c r="R79" s="1"/>
       <c r="S79" s="12"/>
       <c r="T79" s="12">
         <f t="shared" si="18"/>
@@ -10368,7 +10372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10411,7 +10415,7 @@
         <v>0</v>
       </c>
       <c r="Q80" s="12"/>
-      <c r="R80" s="10"/>
+      <c r="R80" s="1"/>
       <c r="S80" s="12"/>
       <c r="T80" s="12">
         <f t="shared" si="18"/>
@@ -10437,7 +10441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10480,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="12"/>
-      <c r="R81" s="10"/>
+      <c r="R81" s="1"/>
       <c r="S81" s="12"/>
       <c r="T81" s="12">
         <f t="shared" si="18"/>
@@ -10506,7 +10510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10520,7 +10524,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10563,7 +10567,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="12"/>
-      <c r="R83" s="10"/>
+      <c r="R83" s="1"/>
       <c r="S83" s="12"/>
       <c r="T83" s="12">
         <f t="shared" si="18"/>
@@ -10589,7 +10593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10632,7 +10636,7 @@
         <v>0</v>
       </c>
       <c r="Q84" s="12"/>
-      <c r="R84" s="10"/>
+      <c r="R84" s="1"/>
       <c r="S84" s="12"/>
       <c r="T84" s="12">
         <f t="shared" si="18"/>
@@ -10658,7 +10662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10701,7 +10705,7 @@
         <v>0</v>
       </c>
       <c r="Q85" s="12"/>
-      <c r="R85" s="10"/>
+      <c r="R85" s="1"/>
       <c r="S85" s="12"/>
       <c r="T85" s="12">
         <f t="shared" si="18"/>
@@ -10727,7 +10731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10770,7 +10774,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="12"/>
-      <c r="R86" s="10"/>
+      <c r="R86" s="1"/>
       <c r="S86" s="12"/>
       <c r="T86" s="12">
         <f t="shared" si="18"/>
@@ -10796,7 +10800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -10839,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="Q87" s="12"/>
-      <c r="R87" s="10"/>
+      <c r="R87" s="1"/>
       <c r="S87" s="12"/>
       <c r="T87" s="12">
         <f t="shared" si="18"/>
@@ -10865,7 +10869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -10908,7 +10912,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="12"/>
-      <c r="R88" s="10"/>
+      <c r="R88" s="1"/>
       <c r="S88" s="12"/>
       <c r="T88" s="12">
         <f t="shared" si="18"/>
@@ -10934,7 +10938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -10977,7 +10981,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="12"/>
-      <c r="R89" s="10"/>
+      <c r="R89" s="1"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12">
         <f t="shared" si="18"/>
@@ -11003,7 +11007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11046,7 +11050,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="12"/>
-      <c r="R90" s="10"/>
+      <c r="R90" s="1"/>
       <c r="S90" s="12"/>
       <c r="T90" s="12">
         <f t="shared" si="18"/>
@@ -11072,7 +11076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11115,7 +11119,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="12"/>
-      <c r="R91" s="10"/>
+      <c r="R91" s="1"/>
       <c r="S91" s="12"/>
       <c r="T91" s="12">
         <f t="shared" si="18"/>
@@ -11141,7 +11145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11155,7 +11159,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11198,7 +11202,7 @@
         <v>0</v>
       </c>
       <c r="Q93" s="12"/>
-      <c r="R93" s="10"/>
+      <c r="R93" s="1"/>
       <c r="S93" s="12"/>
       <c r="T93" s="12">
         <f>IF((P93-Q93)&lt;0,0,(P93-Q93))</f>
@@ -11224,7 +11228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11267,7 +11271,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="12"/>
-      <c r="R94" s="10"/>
+      <c r="R94" s="1"/>
       <c r="S94" s="12"/>
       <c r="T94" s="12">
         <f>IF((P94-Q94)&lt;0,0,(P94-Q94))</f>
@@ -11293,7 +11297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11336,7 +11340,7 @@
         <v>0</v>
       </c>
       <c r="Q95" s="12"/>
-      <c r="R95" s="10"/>
+      <c r="R95" s="1"/>
       <c r="S95" s="12"/>
       <c r="T95" s="12">
         <f>IF((P95-Q95)&lt;0,0,(P95-Q95))</f>
@@ -11362,7 +11366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11405,7 +11409,7 @@
         <v>0</v>
       </c>
       <c r="Q96" s="12"/>
-      <c r="R96" s="10"/>
+      <c r="R96" s="1"/>
       <c r="S96" s="12"/>
       <c r="T96" s="12">
         <f>IF((P96-Q96)&lt;0,0,(P96-Q96))</f>
@@ -11431,7 +11435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11474,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="Q97" s="12"/>
-      <c r="R97" s="10"/>
+      <c r="R97" s="1"/>
       <c r="S97" s="12"/>
       <c r="T97" s="12">
         <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
@@ -11500,7 +11504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11543,7 +11547,7 @@
         <v>0</v>
       </c>
       <c r="Q98" s="12"/>
-      <c r="R98" s="10"/>
+      <c r="R98" s="1"/>
       <c r="S98" s="12"/>
       <c r="T98" s="12">
         <f>IF((P98-Q98)&lt;0,0,(P98-Q98))</f>
@@ -11569,7 +11573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11612,7 +11616,7 @@
         <v>0</v>
       </c>
       <c r="Q99" s="12"/>
-      <c r="R99" s="10"/>
+      <c r="R99" s="1"/>
       <c r="S99" s="12"/>
       <c r="T99" s="12">
         <f>IF((P99-Q99)&lt;0,0,(P99-Q99))</f>
@@ -11638,7 +11642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11681,7 +11685,7 @@
         <v>0</v>
       </c>
       <c r="Q100" s="12"/>
-      <c r="R100" s="10"/>
+      <c r="R100" s="1"/>
       <c r="S100" s="12"/>
       <c r="T100" s="12">
         <f>IF((P100-Q100)&lt;0,0,(P100-Q100))</f>
@@ -11707,7 +11711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11750,7 +11754,7 @@
         <v>0</v>
       </c>
       <c r="Q101" s="12"/>
-      <c r="R101" s="10"/>
+      <c r="R101" s="1"/>
       <c r="S101" s="12"/>
       <c r="T101" s="12">
         <f>IF((P101-Q101)&lt;0,0,(P101-Q101))</f>
@@ -11776,7 +11780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11790,7 +11794,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -11859,7 +11863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -11928,7 +11932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -11997,7 +12001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12066,7 +12070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12135,7 +12139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12204,7 +12208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12273,7 +12277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12342,7 +12346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12353,7 +12357,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12415,7 +12419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12477,7 +12481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12539,7 +12543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12601,7 +12605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12663,7 +12667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12725,7 +12729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12787,7 +12791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12849,7 +12853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -12911,7 +12915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -12973,7 +12977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13035,7 +13039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13097,7 +13101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13159,7 +13163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13221,7 +13225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13283,13 +13287,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
       <c r="D127" s="5"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="29"/>
+      <c r="F127" s="1"/>
       <c r="G127" s="31"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
@@ -13316,7 +13320,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -13342,190 +13346,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 W14:X21 W23:X31 H33:I41 W33:X41 H43:I51 W43:X51 H53:I61 W53:X61 H63:I71 W63:X71 H73:I81 W73:X81 H83:I91 W83:X91 H93:I101 W93:X101 H103:I110 W103:X110 H112:I127 N127:Q127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:Q126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D63:F71 D103:F110 D14:F21 D33:F41 D23:F31 D43:F51 D53:F61 D73:F81 D83:F91 D93:F101 D112:F127 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 R112:R127" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13535,15 +13359,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F93:F101 F53:F61 F5:F12 F23:F31 F14:F21 F33:F41 F43:F51 F63:F71 F73:F81 F83:F91 F103:F110 F112:F127 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R93:R101 R83:R91 R73:R81 R43:R51 R63:R71 R23:R31 R14:R21 R5:R12 R33:R41 R53:R61 R103:R110 R112:R127" xr:uid="{691AD128-B553-48E4-A9B9-D3960492514D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13588,38 +13415,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13658,10 +13485,10 @@
       <c r="L2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>72</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -13694,10 +13521,10 @@
       <c r="X2" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>84</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -13773,7 +13600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13842,7 +13669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13911,7 +13738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -13980,7 +13807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14049,7 +13876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14118,7 +13945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14187,7 +14014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14256,8 +14083,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="R11" s="1"/>
+    </row>
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14326,7 +14155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14395,7 +14224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14464,7 +14293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14533,7 +14362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14602,7 +14431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14671,7 +14500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14740,7 +14569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14809,8 +14638,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="R20" s="1"/>
+    </row>
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14879,7 +14710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -14948,7 +14779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15017,7 +14848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15086,7 +14917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15155,7 +14986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15224,7 +15055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15293,7 +15124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15362,7 +15193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15431,8 +15262,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="R30" s="1"/>
+    </row>
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15501,7 +15334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15570,7 +15403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15639,7 +15472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15708,7 +15541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15777,7 +15610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15846,7 +15679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -15915,7 +15748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -15984,7 +15817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16053,7 +15886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16122,7 +15955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16191,8 +16024,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="R42" s="1"/>
+    </row>
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16261,7 +16096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16330,7 +16165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16399,7 +16234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16468,7 +16303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16537,7 +16372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16606,7 +16441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16675,7 +16510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16744,7 +16579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16813,7 +16648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -16882,7 +16717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -16951,8 +16786,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="R54" s="1"/>
+    </row>
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17021,7 +16858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17090,7 +16927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17159,7 +16996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17228,7 +17065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17297,7 +17134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17366,7 +17203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17435,7 +17272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17504,7 +17341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17573,7 +17410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17642,7 +17479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17711,8 +17548,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="R66" s="1"/>
+    </row>
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17740,7 +17579,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="12"/>
-      <c r="L67" s="10"/>
+      <c r="L67" s="1"/>
       <c r="M67" s="12"/>
       <c r="N67" s="12">
         <f t="shared" si="2"/>
@@ -17755,7 +17594,7 @@
         <v>0</v>
       </c>
       <c r="Q67" s="12"/>
-      <c r="R67" s="10"/>
+      <c r="R67" s="1"/>
       <c r="S67" s="12"/>
       <c r="T67" s="12">
         <f t="shared" si="4"/>
@@ -17781,7 +17620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17809,7 +17648,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="12"/>
-      <c r="L68" s="10"/>
+      <c r="L68" s="1"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12">
         <f t="shared" si="2"/>
@@ -17824,7 +17663,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="12"/>
-      <c r="R68" s="10"/>
+      <c r="R68" s="1"/>
       <c r="S68" s="12"/>
       <c r="T68" s="12">
         <f t="shared" si="4"/>
@@ -17850,7 +17689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -17878,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="12"/>
-      <c r="L69" s="10"/>
+      <c r="L69" s="1"/>
       <c r="M69" s="12"/>
       <c r="N69" s="12">
         <f t="shared" si="2"/>
@@ -17893,7 +17732,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="12"/>
-      <c r="R69" s="10"/>
+      <c r="R69" s="1"/>
       <c r="S69" s="12"/>
       <c r="T69" s="12">
         <f t="shared" si="4"/>
@@ -17919,7 +17758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -17947,7 +17786,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="12"/>
-      <c r="L70" s="10"/>
+      <c r="L70" s="1"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
         <f t="shared" si="2"/>
@@ -17962,7 +17801,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="12"/>
-      <c r="R70" s="10"/>
+      <c r="R70" s="1"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12">
         <f t="shared" si="4"/>
@@ -17988,7 +17827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18016,7 +17855,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="12"/>
-      <c r="L71" s="10"/>
+      <c r="L71" s="1"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
         <f t="shared" ref="N71:N77" si="14">IF((J71-K71)&lt;0,0,(J71-K71))</f>
@@ -18031,7 +17870,7 @@
         <v>0</v>
       </c>
       <c r="Q71" s="12"/>
-      <c r="R71" s="10"/>
+      <c r="R71" s="1"/>
       <c r="S71" s="12"/>
       <c r="T71" s="12">
         <f t="shared" si="4"/>
@@ -18057,7 +17896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18085,7 +17924,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="12"/>
-      <c r="L72" s="10"/>
+      <c r="L72" s="1"/>
       <c r="M72" s="12"/>
       <c r="N72" s="12">
         <f t="shared" si="14"/>
@@ -18100,7 +17939,7 @@
         <v>0</v>
       </c>
       <c r="Q72" s="12"/>
-      <c r="R72" s="10"/>
+      <c r="R72" s="1"/>
       <c r="S72" s="12"/>
       <c r="T72" s="12">
         <f t="shared" si="4"/>
@@ -18126,7 +17965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18154,7 +17993,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="12"/>
-      <c r="L73" s="10"/>
+      <c r="L73" s="1"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12">
         <f t="shared" si="14"/>
@@ -18169,7 +18008,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="12"/>
-      <c r="R73" s="10"/>
+      <c r="R73" s="1"/>
       <c r="S73" s="12"/>
       <c r="T73" s="12">
         <f>IF((P73-Q73)&lt;0,0,(P73-Q73))</f>
@@ -18195,7 +18034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18223,7 +18062,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="12"/>
-      <c r="L74" s="10"/>
+      <c r="L74" s="1"/>
       <c r="M74" s="12"/>
       <c r="N74" s="12">
         <f t="shared" si="14"/>
@@ -18238,7 +18077,7 @@
         <v>0</v>
       </c>
       <c r="Q74" s="12"/>
-      <c r="R74" s="10"/>
+      <c r="R74" s="1"/>
       <c r="S74" s="12"/>
       <c r="T74" s="12">
         <f t="shared" ref="T74:T122" si="16">IF((P74-Q74)&lt;0,0,(P74-Q74))</f>
@@ -18264,7 +18103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18292,7 +18131,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="12"/>
-      <c r="L75" s="10"/>
+      <c r="L75" s="1"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
         <f t="shared" si="14"/>
@@ -18307,7 +18146,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="12"/>
-      <c r="R75" s="10"/>
+      <c r="R75" s="1"/>
       <c r="S75" s="12"/>
       <c r="T75" s="12">
         <f t="shared" si="16"/>
@@ -18333,7 +18172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18361,7 +18200,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="12"/>
-      <c r="L76" s="10"/>
+      <c r="L76" s="1"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
         <f t="shared" si="14"/>
@@ -18376,7 +18215,7 @@
         <v>0</v>
       </c>
       <c r="Q76" s="12"/>
-      <c r="R76" s="10"/>
+      <c r="R76" s="1"/>
       <c r="S76" s="12"/>
       <c r="T76" s="12">
         <f>IF((P76-Q76)&lt;0,0,(P76-Q76))</f>
@@ -18402,7 +18241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18430,7 +18269,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="12"/>
-      <c r="L77" s="10"/>
+      <c r="L77" s="1"/>
       <c r="M77" s="12"/>
       <c r="N77" s="12">
         <f t="shared" si="14"/>
@@ -18445,7 +18284,7 @@
         <v>0</v>
       </c>
       <c r="Q77" s="12"/>
-      <c r="R77" s="10"/>
+      <c r="R77" s="1"/>
       <c r="S77" s="12"/>
       <c r="T77" s="12">
         <f t="shared" si="16"/>
@@ -18471,8 +18310,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="R78" s="1"/>
+    </row>
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18500,7 +18341,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="12"/>
-      <c r="L79" s="10"/>
+      <c r="L79" s="1"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
         <f t="shared" ref="N74:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
@@ -18515,7 +18356,7 @@
         <v>0</v>
       </c>
       <c r="Q79" s="12"/>
-      <c r="R79" s="10"/>
+      <c r="R79" s="1"/>
       <c r="S79" s="12"/>
       <c r="T79" s="12">
         <f t="shared" si="16"/>
@@ -18541,7 +18382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18569,7 +18410,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="12"/>
-      <c r="L80" s="10"/>
+      <c r="L80" s="1"/>
       <c r="M80" s="12"/>
       <c r="N80" s="12">
         <f t="shared" si="20"/>
@@ -18584,7 +18425,7 @@
         <v>0</v>
       </c>
       <c r="Q80" s="12"/>
-      <c r="R80" s="10"/>
+      <c r="R80" s="1"/>
       <c r="S80" s="12"/>
       <c r="T80" s="12">
         <f t="shared" si="16"/>
@@ -18610,7 +18451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18638,7 +18479,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="12"/>
-      <c r="L81" s="10"/>
+      <c r="L81" s="1"/>
       <c r="M81" s="12"/>
       <c r="N81" s="12">
         <f t="shared" si="20"/>
@@ -18653,7 +18494,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="12"/>
-      <c r="R81" s="10"/>
+      <c r="R81" s="1"/>
       <c r="S81" s="12"/>
       <c r="T81" s="12">
         <f t="shared" si="16"/>
@@ -18679,7 +18520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18707,7 +18548,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="12"/>
-      <c r="L82" s="10"/>
+      <c r="L82" s="1"/>
       <c r="M82" s="12"/>
       <c r="N82" s="12">
         <f t="shared" si="20"/>
@@ -18722,7 +18563,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="12"/>
-      <c r="R82" s="10"/>
+      <c r="R82" s="1"/>
       <c r="S82" s="12"/>
       <c r="T82" s="12">
         <f t="shared" si="16"/>
@@ -18748,7 +18589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18776,7 +18617,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="12"/>
-      <c r="L83" s="10"/>
+      <c r="L83" s="1"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12">
         <f t="shared" si="20"/>
@@ -18791,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="12"/>
-      <c r="R83" s="10"/>
+      <c r="R83" s="1"/>
       <c r="S83" s="12"/>
       <c r="T83" s="12">
         <f t="shared" si="16"/>
@@ -18817,7 +18658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -18845,7 +18686,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="12"/>
-      <c r="L84" s="10"/>
+      <c r="L84" s="1"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12">
         <f t="shared" ref="N84:N89" si="24">IF((J84-K84)&lt;0,0,(J84-K84))</f>
@@ -18860,7 +18701,7 @@
         <v>0</v>
       </c>
       <c r="Q84" s="12"/>
-      <c r="R84" s="10"/>
+      <c r="R84" s="1"/>
       <c r="S84" s="12"/>
       <c r="T84" s="12">
         <f t="shared" si="16"/>
@@ -18886,7 +18727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -18914,7 +18755,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="12"/>
-      <c r="L85" s="10"/>
+      <c r="L85" s="1"/>
       <c r="M85" s="12"/>
       <c r="N85" s="12">
         <f t="shared" si="24"/>
@@ -18929,7 +18770,7 @@
         <v>0</v>
       </c>
       <c r="Q85" s="12"/>
-      <c r="R85" s="10"/>
+      <c r="R85" s="1"/>
       <c r="S85" s="12"/>
       <c r="T85" s="12">
         <f>IF((P85-Q85)&lt;0,0,(P85-Q85))</f>
@@ -18955,7 +18796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -18983,7 +18824,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="12"/>
-      <c r="L86" s="10"/>
+      <c r="L86" s="1"/>
       <c r="M86" s="12"/>
       <c r="N86" s="12">
         <f t="shared" si="24"/>
@@ -18998,7 +18839,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="12"/>
-      <c r="R86" s="10"/>
+      <c r="R86" s="1"/>
       <c r="S86" s="12"/>
       <c r="T86" s="12">
         <f t="shared" si="16"/>
@@ -19024,7 +18865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19052,7 +18893,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="12"/>
-      <c r="L87" s="10"/>
+      <c r="L87" s="1"/>
       <c r="M87" s="12"/>
       <c r="N87" s="12">
         <f t="shared" si="24"/>
@@ -19067,7 +18908,7 @@
         <v>0</v>
       </c>
       <c r="Q87" s="12"/>
-      <c r="R87" s="10"/>
+      <c r="R87" s="1"/>
       <c r="S87" s="12"/>
       <c r="T87" s="12">
         <f t="shared" si="16"/>
@@ -19093,7 +18934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19121,7 +18962,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="12"/>
-      <c r="L88" s="10"/>
+      <c r="L88" s="1"/>
       <c r="M88" s="12"/>
       <c r="N88" s="12">
         <f t="shared" si="24"/>
@@ -19136,7 +18977,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="12"/>
-      <c r="R88" s="10"/>
+      <c r="R88" s="1"/>
       <c r="S88" s="12"/>
       <c r="T88" s="12">
         <f>IF((P88-Q88)&lt;0,0,(P88-Q88))</f>
@@ -19162,7 +19003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19190,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="12"/>
-      <c r="L89" s="10"/>
+      <c r="L89" s="1"/>
       <c r="M89" s="12"/>
       <c r="N89" s="12">
         <f t="shared" si="24"/>
@@ -19205,7 +19046,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="12"/>
-      <c r="R89" s="10"/>
+      <c r="R89" s="1"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12">
         <f t="shared" si="16"/>
@@ -19231,8 +19072,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="R90" s="1"/>
+    </row>
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19260,7 +19103,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="12"/>
-      <c r="L91" s="10"/>
+      <c r="L91" s="1"/>
       <c r="M91" s="12"/>
       <c r="N91" s="12">
         <f t="shared" si="20"/>
@@ -19275,7 +19118,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="12"/>
-      <c r="R91" s="10"/>
+      <c r="R91" s="1"/>
       <c r="S91" s="12"/>
       <c r="T91" s="12">
         <f t="shared" si="16"/>
@@ -19301,7 +19144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19329,7 +19172,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="12"/>
-      <c r="L92" s="10"/>
+      <c r="L92" s="1"/>
       <c r="M92" s="12"/>
       <c r="N92" s="12">
         <f t="shared" si="20"/>
@@ -19344,7 +19187,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="12"/>
-      <c r="R92" s="10"/>
+      <c r="R92" s="1"/>
       <c r="S92" s="12"/>
       <c r="T92" s="12">
         <f t="shared" si="16"/>
@@ -19370,7 +19213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19398,7 +19241,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="12"/>
-      <c r="L93" s="10"/>
+      <c r="L93" s="1"/>
       <c r="M93" s="12"/>
       <c r="N93" s="12">
         <f t="shared" si="20"/>
@@ -19413,7 +19256,7 @@
         <v>0</v>
       </c>
       <c r="Q93" s="12"/>
-      <c r="R93" s="10"/>
+      <c r="R93" s="1"/>
       <c r="S93" s="12"/>
       <c r="T93" s="12">
         <f t="shared" si="16"/>
@@ -19439,7 +19282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19467,7 +19310,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="12"/>
-      <c r="L94" s="10"/>
+      <c r="L94" s="1"/>
       <c r="M94" s="12"/>
       <c r="N94" s="12">
         <f t="shared" si="20"/>
@@ -19482,7 +19325,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="12"/>
-      <c r="R94" s="10"/>
+      <c r="R94" s="1"/>
       <c r="S94" s="12"/>
       <c r="T94" s="12">
         <f t="shared" si="16"/>
@@ -19508,7 +19351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19536,7 +19379,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="12"/>
-      <c r="L95" s="10"/>
+      <c r="L95" s="1"/>
       <c r="M95" s="12"/>
       <c r="N95" s="12">
         <f t="shared" si="20"/>
@@ -19551,7 +19394,7 @@
         <v>0</v>
       </c>
       <c r="Q95" s="12"/>
-      <c r="R95" s="10"/>
+      <c r="R95" s="1"/>
       <c r="S95" s="12"/>
       <c r="T95" s="12">
         <f t="shared" si="16"/>
@@ -19577,7 +19420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19605,7 +19448,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="12"/>
-      <c r="L96" s="10"/>
+      <c r="L96" s="1"/>
       <c r="M96" s="12"/>
       <c r="N96" s="12">
         <f t="shared" si="20"/>
@@ -19620,7 +19463,7 @@
         <v>0</v>
       </c>
       <c r="Q96" s="12"/>
-      <c r="R96" s="10"/>
+      <c r="R96" s="1"/>
       <c r="S96" s="12"/>
       <c r="T96" s="12">
         <f t="shared" si="16"/>
@@ -19646,7 +19489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19674,7 +19517,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="12"/>
-      <c r="L97" s="10"/>
+      <c r="L97" s="1"/>
       <c r="M97" s="12"/>
       <c r="N97" s="12">
         <f t="shared" ref="N97:N101" si="26">IF((J97-K97)&lt;0,0,(J97-K97))</f>
@@ -19689,7 +19532,7 @@
         <v>0</v>
       </c>
       <c r="Q97" s="12"/>
-      <c r="R97" s="10"/>
+      <c r="R97" s="1"/>
       <c r="S97" s="12"/>
       <c r="T97" s="12">
         <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
@@ -19715,7 +19558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19743,7 +19586,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="12"/>
-      <c r="L98" s="10"/>
+      <c r="L98" s="1"/>
       <c r="M98" s="12"/>
       <c r="N98" s="12">
         <f t="shared" si="26"/>
@@ -19758,7 +19601,7 @@
         <v>0</v>
       </c>
       <c r="Q98" s="12"/>
-      <c r="R98" s="10"/>
+      <c r="R98" s="1"/>
       <c r="S98" s="12"/>
       <c r="T98" s="12">
         <f t="shared" si="16"/>
@@ -19784,7 +19627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19812,7 +19655,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="12"/>
-      <c r="L99" s="10"/>
+      <c r="L99" s="1"/>
       <c r="M99" s="12"/>
       <c r="N99" s="12">
         <f t="shared" si="26"/>
@@ -19827,7 +19670,7 @@
         <v>0</v>
       </c>
       <c r="Q99" s="12"/>
-      <c r="R99" s="10"/>
+      <c r="R99" s="1"/>
       <c r="S99" s="12"/>
       <c r="T99" s="12">
         <f t="shared" si="16"/>
@@ -19853,7 +19696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -19881,7 +19724,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="12"/>
-      <c r="L100" s="10"/>
+      <c r="L100" s="1"/>
       <c r="M100" s="12"/>
       <c r="N100" s="12">
         <f t="shared" si="26"/>
@@ -19896,7 +19739,7 @@
         <v>0</v>
       </c>
       <c r="Q100" s="12"/>
-      <c r="R100" s="10"/>
+      <c r="R100" s="1"/>
       <c r="S100" s="12"/>
       <c r="T100" s="12">
         <f>IF((P100-Q100)&lt;0,0,(P100-Q100))</f>
@@ -19922,7 +19765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -19950,7 +19793,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="12"/>
-      <c r="L101" s="10"/>
+      <c r="L101" s="1"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12">
         <f t="shared" si="26"/>
@@ -19965,7 +19808,7 @@
         <v>0</v>
       </c>
       <c r="Q101" s="12"/>
-      <c r="R101" s="10"/>
+      <c r="R101" s="1"/>
       <c r="S101" s="12"/>
       <c r="T101" s="12">
         <f t="shared" si="16"/>
@@ -19991,8 +19834,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="R102" s="1"/>
+    </row>
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20020,7 +19865,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="12"/>
-      <c r="L103" s="10"/>
+      <c r="L103" s="1"/>
       <c r="M103" s="12"/>
       <c r="N103" s="12">
         <f t="shared" si="20"/>
@@ -20035,7 +19880,7 @@
         <v>0</v>
       </c>
       <c r="Q103" s="12"/>
-      <c r="R103" s="10"/>
+      <c r="R103" s="1"/>
       <c r="S103" s="12"/>
       <c r="T103" s="12">
         <f t="shared" si="16"/>
@@ -20061,7 +19906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20089,7 +19934,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="12"/>
-      <c r="L104" s="10"/>
+      <c r="L104" s="1"/>
       <c r="M104" s="12"/>
       <c r="N104" s="12">
         <f t="shared" si="20"/>
@@ -20104,7 +19949,7 @@
         <v>0</v>
       </c>
       <c r="Q104" s="12"/>
-      <c r="R104" s="10"/>
+      <c r="R104" s="1"/>
       <c r="S104" s="12"/>
       <c r="T104" s="12">
         <f t="shared" si="16"/>
@@ -20130,7 +19975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20158,7 +20003,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="12"/>
-      <c r="L105" s="10"/>
+      <c r="L105" s="1"/>
       <c r="M105" s="12"/>
       <c r="N105" s="12">
         <f t="shared" si="20"/>
@@ -20173,7 +20018,7 @@
         <v>0</v>
       </c>
       <c r="Q105" s="12"/>
-      <c r="R105" s="10"/>
+      <c r="R105" s="1"/>
       <c r="S105" s="12"/>
       <c r="T105" s="12">
         <f t="shared" si="16"/>
@@ -20199,7 +20044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20227,7 +20072,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="12"/>
-      <c r="L106" s="10"/>
+      <c r="L106" s="1"/>
       <c r="M106" s="12"/>
       <c r="N106" s="12">
         <f t="shared" si="20"/>
@@ -20242,7 +20087,7 @@
         <v>0</v>
       </c>
       <c r="Q106" s="12"/>
-      <c r="R106" s="10"/>
+      <c r="R106" s="1"/>
       <c r="S106" s="12"/>
       <c r="T106" s="12">
         <f t="shared" si="16"/>
@@ -20268,7 +20113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20296,7 +20141,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="12"/>
-      <c r="L107" s="10"/>
+      <c r="L107" s="1"/>
       <c r="M107" s="12"/>
       <c r="N107" s="12">
         <f t="shared" si="20"/>
@@ -20311,7 +20156,7 @@
         <v>0</v>
       </c>
       <c r="Q107" s="12"/>
-      <c r="R107" s="10"/>
+      <c r="R107" s="1"/>
       <c r="S107" s="12"/>
       <c r="T107" s="12">
         <f t="shared" si="16"/>
@@ -20337,7 +20182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20365,7 +20210,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="12"/>
-      <c r="L108" s="10"/>
+      <c r="L108" s="1"/>
       <c r="M108" s="12"/>
       <c r="N108" s="12">
         <f t="shared" si="20"/>
@@ -20380,7 +20225,7 @@
         <v>0</v>
       </c>
       <c r="Q108" s="12"/>
-      <c r="R108" s="10"/>
+      <c r="R108" s="1"/>
       <c r="S108" s="12"/>
       <c r="T108" s="12">
         <f t="shared" si="16"/>
@@ -20406,7 +20251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20434,7 +20279,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="12"/>
-      <c r="L109" s="10"/>
+      <c r="L109" s="1"/>
       <c r="M109" s="12"/>
       <c r="N109" s="12">
         <f t="shared" ref="N109:N113" si="28">IF((J109-K109)&lt;0,0,(J109-K109))</f>
@@ -20449,7 +20294,7 @@
         <v>0</v>
       </c>
       <c r="Q109" s="12"/>
-      <c r="R109" s="10"/>
+      <c r="R109" s="1"/>
       <c r="S109" s="12"/>
       <c r="T109" s="12">
         <f>IF((P109-Q109)&lt;0,0,(P109-Q109))</f>
@@ -20475,7 +20320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20503,7 +20348,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="12"/>
-      <c r="L110" s="10"/>
+      <c r="L110" s="1"/>
       <c r="M110" s="12"/>
       <c r="N110" s="12">
         <f t="shared" si="28"/>
@@ -20518,7 +20363,7 @@
         <v>0</v>
       </c>
       <c r="Q110" s="12"/>
-      <c r="R110" s="10"/>
+      <c r="R110" s="1"/>
       <c r="S110" s="12"/>
       <c r="T110" s="12">
         <f t="shared" si="16"/>
@@ -20544,7 +20389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20572,7 +20417,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="12"/>
-      <c r="L111" s="10"/>
+      <c r="L111" s="1"/>
       <c r="M111" s="12"/>
       <c r="N111" s="12">
         <f t="shared" si="28"/>
@@ -20587,7 +20432,7 @@
         <v>0</v>
       </c>
       <c r="Q111" s="12"/>
-      <c r="R111" s="10"/>
+      <c r="R111" s="1"/>
       <c r="S111" s="12"/>
       <c r="T111" s="12">
         <f t="shared" si="16"/>
@@ -20613,7 +20458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20641,7 +20486,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="12"/>
-      <c r="L112" s="10"/>
+      <c r="L112" s="1"/>
       <c r="M112" s="12"/>
       <c r="N112" s="12">
         <f t="shared" si="28"/>
@@ -20656,7 +20501,7 @@
         <v>0</v>
       </c>
       <c r="Q112" s="12"/>
-      <c r="R112" s="10"/>
+      <c r="R112" s="1"/>
       <c r="S112" s="12"/>
       <c r="T112" s="12">
         <f>IF((P112-Q112)&lt;0,0,(P112-Q112))</f>
@@ -20682,7 +20527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20710,7 +20555,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="12"/>
-      <c r="L113" s="10"/>
+      <c r="L113" s="1"/>
       <c r="M113" s="12"/>
       <c r="N113" s="12">
         <f t="shared" si="28"/>
@@ -20725,7 +20570,7 @@
         <v>0</v>
       </c>
       <c r="Q113" s="12"/>
-      <c r="R113" s="10"/>
+      <c r="R113" s="1"/>
       <c r="S113" s="12"/>
       <c r="T113" s="12">
         <f t="shared" si="16"/>
@@ -20751,7 +20596,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
+    <row r="114" spans="1:28" s="7" customFormat="1" ht="19.5">
+      <c r="R114" s="1"/>
+    </row>
     <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>23</v>
@@ -21024,7 +20871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21991,7 +21838,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R3 N3:O10 V2:X10 T3:U10 N12:Q19 T12:X19 Z3:AA10 Z12:AA19 N21:Q29 T21:X29 Z21:AA29 T31:X41 Z31:AA41 T43:X53 Z43:AA53 T55:X65 Z55:AA65 T67:X77 Z67:AA77 T79:X89 Z79:AA89 T91:X101 Z91:AA101 T103:X113 Z103:AA113 N115:Q122 T115:X122 Z115:AA122 D103:F113 N31:Q41 N43:Q53 N55:Q65 N67:Q77 N79:Q89 N91:Q101 N103:Q113 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H67:L77 H79:L89 H91:L101 H103:L113 H115:L122 P4:Q10 R4:R122" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22001,12 +21848,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 X115:X122 R114 R102 R90 R78 R66 R54 R42 R30 R20 R11" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 L91:L101 L103:L113 L115:L122 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10" xr:uid="{4A608AFD-173D-448E-B164-C5E2E04BBA6D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
